--- a/jpcore-r4/feature/test-claude-opus/StructureDefinition-jp-servicerequest-common.xlsx
+++ b/jpcore-r4/feature/test-claude-opus/StructureDefinition-jp-servicerequest-common.xlsx
@@ -449,7 +449,7 @@
     <t>ServiceRequest.meta.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition)
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -487,7 +487,7 @@
     <t>医療プライバシーおよびセキュリティ分類システムからのセキュリティラベル。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
   </si>
   <si>
     <t>Meta.security</t>
@@ -545,7 +545,7 @@
     <t>人間の言語。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -661,7 +661,7 @@
     <t>ServiceRequest.instantiatesCanonical</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(ActivityDefinition|PlanDefinition)
+    <t xml:space="preserve">canonical(ActivityDefinition|4.0.1|PlanDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -866,7 +866,7 @@
     <t>要求されたサービスの分類。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/servicerequest-category</t>
+    <t>http://hl7.org/fhir/ValueSet/servicerequest-category|4.0.1</t>
   </si>
   <si>
     <t>RF1-5</t>
@@ -952,7 +952,7 @@
     <t>指定された個人、組織、または医療サービスによって実施できるテストやサービスのコード。ラボの場合、LOINCが（preferred）[http://build.fhir.org/terminologies.html#preferred]であり、LOINCオーダーコードを使用した値セットが[こちら]（valueset-diagnostic-requests.html）で利用可能です。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/procedure-code</t>
+    <t>http://hl7.org/fhir/ValueSet/procedure-code|4.0.1</t>
   </si>
   <si>
     <t>Request.code</t>
@@ -989,7 +989,7 @@
     <t>注文コンテキストに基づくコード化された注文詳細。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/servicerequest-orderdetail</t>
+    <t>http://hl7.org/fhir/ValueSet/servicerequest-orderdetail|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">prr-1
@@ -1129,7 +1129,7 @@
     <t>手続きを実行する前に満たされる必要がある前提条件を示すコード化された概念。たとえば、「痛み」、「フレアアップ時」など。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medication-as-needed-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/medication-as-needed-reason|4.0.1</t>
   </si>
   <si>
     <t>boolean: precondition.negationInd (inversed - so negationInd = true means asNeeded=false CodeableConcept: precondition.observationEventCriterion[code="Assertion"].value</t>
@@ -1224,7 +1224,7 @@
     <t>初診医師」、「チームコーディネーター」、「介護者」など、ケアチーム内の個人の具体的責任を示します。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/participant-role</t>
+    <t>http://hl7.org/fhir/ValueSet/participant-role|4.0.1</t>
   </si>
   <si>
     <t>Request.performerType</t>
@@ -1317,7 +1317,7 @@
     <t>サービス調査の依頼理由を正当化する診断または問題コード。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/procedure-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/procedure-reason|4.0.1</t>
   </si>
   <si>
     <t>Request.reasonCode</t>
@@ -1386,7 +1386,7 @@
 AOE</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1452,7 +1452,7 @@
     <t>解剖学的位置を記述するコード。左右対称性を含む場合があります。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+    <t>http://hl7.org/fhir/ValueSet/body-site|4.0.1</t>
   </si>
   <si>
     <t>targetSiteCode</t>
@@ -1498,7 +1498,7 @@
     <t>ServiceRequest.relevantHistory</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Provenance)
+    <t xml:space="preserve">Reference(Provenance|4.0.1)
 </t>
   </si>
   <si>
